--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:42:43+00:00</t>
+    <t>2026-06-22T14:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:38:01+00:00</t>
+    <t>2026-06-29T12:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:42:10+00:00</t>
+    <t>2026-07-07T09:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T09:34:50+00:00</t>
+    <t>2026-07-16T11:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:52:18+00:00</t>
+    <t>2026-07-16T13:43:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T13:43:45+00:00</t>
+    <t>2026-07-16T16:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T16:12:39+00:00</t>
+    <t>2026-07-20T14:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:23:22+00:00</t>
+    <t>2026-08-12T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:16:17+00:00</t>
+    <t>2026-08-13T08:08:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:08:00+00:00</t>
+    <t>2026-08-13T08:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="379">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:33:40+00:00</t>
+    <t>2026-08-13T08:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Medication|4.0.1</t>
+    <t>http://hl7.eu/fhir/base/StructureDefinition/medication-eu-core|2.0.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -491,10 +491,26 @@
     <t>Medication classification/category. Allows the product to be classified by various systems, e.g ATC, narcotic class, legal status of supply, etc..</t>
   </si>
   <si>
-    <t>Medication.extension:conditionnement</t>
-  </si>
-  <si>
-    <t>conditionnement</t>
+    <t>Medication.extension:sizeOfItem</t>
+  </si>
+  <si>
+    <t>sizeOfItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-sizeofitem|1.0.0-comment-2}
+</t>
+  </si>
+  <si>
+    <t>Size of one item (for example, in a pack of 5 vials, this would represent the size of 1 vial)</t>
+  </si>
+  <si>
+    <t>Size of a manufactured item or unit of presentation. For example, size of one vial in a package that may contain several vials.</t>
+  </si>
+  <si>
+    <t>Medication.extension:characteristic</t>
+  </si>
+  <si>
+    <t>characteristic</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-characteristic|1.0.0-comment-2}
@@ -507,6 +523,193 @@
     <t>Any characteristic of the medicinal product prescribed or dispensed (for example, price, textual package description, special program information, etc)</t>
   </si>
   <si>
+    <t>Medication.extension:unitOfPresentation</t>
+  </si>
+  <si>
+    <t>unitOfPresentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-unitofpresentation|1.0.0-comment-2}
+</t>
+  </si>
+  <si>
+    <t>Unit of presentation of the product (e.g. tablet, vial, ampoule, etc)</t>
+  </si>
+  <si>
+    <t>Unit of presentation, typically describing the smallest countable package item (e.g tablet, vial, ampoule, etc). Unit of presentation is also often used in describing pack size and the denominator of strength. If the size of presentation unit is relevant, it should be described in sizeOfItem extension.</t>
+  </si>
+  <si>
+    <t>Medication.extension:packageType</t>
+  </si>
+  <si>
+    <t>packageType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/medication-package-type|1.3.0}
+</t>
+  </si>
+  <si>
+    <t>Type of container. This information is more relevant in cases when the packaging has an impact on administration of the product (e.g. pre-filled syringe)</t>
+  </si>
+  <si>
+    <t>This extension applies to Medication and expresses the type of the container for the product (e.g. bottle, unit-dose blister, pre-filled pen).</t>
+  </si>
+  <si>
+    <t>Medication.extension:device</t>
+  </si>
+  <si>
+    <t>device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-device|1.0.0-comment-2}
+</t>
+  </si>
+  <si>
+    <t>Device, typically an administration device, included in the product.</t>
+  </si>
+  <si>
+    <t>Device, typically an administration device, included in the medicinal product.</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.id</t>
+  </si>
+  <si>
+    <t>Medication.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension</t>
+  </si>
+  <si>
+    <t>Medication.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension:device</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension:device.id</t>
+  </si>
+  <si>
+    <t>Medication.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension:device.extension</t>
+  </si>
+  <si>
+    <t>Medication.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension:device.url</t>
+  </si>
+  <si>
+    <t>Medication.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension:device.value[x]</t>
+  </si>
+  <si>
+    <t>Medication.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://terminology.ehdsi.eu/ValueSet/eHDSIPackage</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension:quantity</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>Number of defined devices in te package</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension:quantity.id</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension:quantity.extension</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension:quantity.url</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.extension:quantity.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.url</t>
+  </si>
+  <si>
+    <t>Medication.extension.url</t>
+  </si>
+  <si>
+    <t>https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-device</t>
+  </si>
+  <si>
+    <t>Medication.extension:device.value[x]</t>
+  </si>
+  <si>
+    <t>Medication.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
     <t>Medication.modifierExtension</t>
   </si>
   <si>
@@ -537,7 +740,7 @@
 </t>
   </si>
   <si>
-    <t>Business identifier for this medication</t>
+    <t>Identifier for the medicinal product, its generic representation, or packaged product (e.g. EMA PMS ID on product or package level)</t>
   </si>
   <si>
     <t>Business identifier for this medication.</t>
@@ -555,10 +758,6 @@
     <t>Medication.code</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Code du produit de santé</t>
   </si>
   <si>
@@ -566,9 +765,6 @@
   </si>
   <si>
     <t>Depending on the context of use, the code that was actually selected by the user (prescriber, dispenser, etc.) will have the coding.userSelected set to true.  As described in the coding datatype: "A coding may be marked as a "userSelected" if a user selected the particular coded value in a user interface (e.g. the user selects an item in a pick-list). If a user selected coding exists, it is the preferred choice for performing translations etc. Other codes can only be literal translations to alternative code systems, or codes at a lower level of granularity (e.g. a generic code for a vendor-specific primary one).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>A coded concept that defines the type of a medication.</t>
@@ -596,22 +792,6 @@
     <t>Medication.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Medication.code.extension</t>
   </si>
   <si>
@@ -619,12 +799,6 @@
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Medication.code.coding</t>
@@ -713,7 +887,7 @@
 </t>
   </si>
   <si>
-    <t>Manufacturer of the item</t>
+    <t>Marketing authorisation holder of the medicinal product. If the product does not have a marketing authorisation, the manufactured information may be used. It is sufficient to populate only name and optionally an identifier of the organisation.</t>
   </si>
   <si>
     <t>Describes the details of the manufacturer of the medication product.  This is not intended to represent the distributor of a medication product.</t>
@@ -764,7 +938,7 @@
 </t>
   </si>
   <si>
-    <t>Amount of drug in package</t>
+    <t>Amount of the medication (for example, in a package or a vial)</t>
   </si>
   <si>
     <t>Specific amount of the drug in the packaged product.  For example, when specifying a product that has the same strength (For example, Insulin glargine 100 unit per mL solution for injection), this attribute provides additional clarification of the package amount (For example, 3 mL, 10mL, etc.).</t>
@@ -780,7 +954,7 @@
 </t>
   </si>
   <si>
-    <t>Active or inactive ingredient</t>
+    <t>Ingredient or a part product. For combination packs, each ingredient can be a separate manufactured item with its own ingredients, dose form, and strength</t>
   </si>
   <si>
     <t>Identifies a particular constituent of interest in the product.</t>
@@ -844,45 +1018,6 @@
     <t>RXC-2-Component Code  if medication: RXO-1-Requested Give Code / RXE-2-Give Code / RXD-2-Dispense/Give Code / RXG-4-Give Code / RXA-5-Administered Code</t>
   </si>
   <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept</t>
-  </si>
-  <si>
-    <t>itemCodeableConcept</t>
-  </si>
-  <si>
-    <t>Code SMS de la substance active</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/terminologie-sms?vs|20241114120000</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].id</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].extension</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].coding</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x]:itemCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Medication.ingredient.item[x].text</t>
-  </si>
-  <si>
-    <t>Nom de la substance</t>
-  </si>
-  <si>
     <t>Medication.ingredient.item[x]:itemReference</t>
   </si>
   <si>
@@ -893,6 +1028,45 @@
 </t>
   </si>
   <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>Code SMS de la substance active</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/terminologie-sms?vs|20241114120000</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].coding</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x].text</t>
+  </si>
+  <si>
+    <t>Nom de la substance</t>
+  </si>
+  <si>
     <t>Medication.ingredient.isActive</t>
   </si>
   <si>
@@ -900,7 +1074,7 @@
 </t>
   </si>
   <si>
-    <t>Active ingredient indicator</t>
+    <t>Active ingredient indicator. By default, only active ingredients are expected - therefore, the default value is true.</t>
   </si>
   <si>
     <t>Indication of whether this ingredient affects the therapeutic action of the drug.</t>
@@ -919,7 +1093,7 @@
     <t>Quantité de substance présente dans le médicament</t>
   </si>
   <si>
-    <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
+    <t>Definitional resources should be used for specifying the different types of strengths: presentation; concentration.</t>
   </si>
   <si>
     <t>//element(*,DrugCodedType)/Strength</t>
@@ -934,11 +1108,23 @@
     <t>Medication.ingredient.strength.extension</t>
   </si>
   <si>
+    <t>Medication.ingredient.strength.extension:basisOfStrengthSubstance</t>
+  </si>
+  <si>
+    <t>basisOfStrengthSubstance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-medication-strengthsubstance|1.0.0-comment-2}
+</t>
+  </si>
+  <si>
+    <t>Substance for which the strength is provided (this could be different from the precise active ingredient).</t>
+  </si>
+  <si>
+    <t>Substance for marking the basis of strength. When the precise active ingredient is a salt, the strength is often provided for the active moiety (basis of strength).</t>
+  </si>
+  <si>
     <t>Medication.ingredient.strength.numerator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
   </si>
   <si>
     <t>Numerator value</t>
@@ -1327,12 +1513,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN46"/>
+  <dimension ref="A1:AN65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.4140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="54.796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.77734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="18.3359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="21.7734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1340,7 +1526,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2643,7 +2829,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>78</v>
@@ -2744,11 +2930,13 @@
         <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2761,26 +2949,22 @@
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="O13" t="s" s="2">
-        <v>161</v>
-      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>78</v>
       </c>
@@ -2828,7 +3012,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2837,7 +3021,7 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>139</v>
@@ -2846,7 +3030,7 @@
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -2857,12 +3041,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>78</v>
       </c>
@@ -2871,7 +3057,7 @@
         <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>78</v>
@@ -2880,20 +3066,18 @@
         <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -2942,7 +3126,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -2951,19 +3135,19 @@
         <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
@@ -2971,18 +3155,20 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>88</v>
@@ -2994,20 +3180,18 @@
         <v>78</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>78</v>
@@ -3032,13 +3216,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -3056,41 +3240,43 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="D16" t="s" s="2">
         <v>78</v>
       </c>
@@ -3099,7 +3285,7 @@
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -3111,13 +3297,13 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3168,25 +3354,25 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -3197,21 +3383,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
@@ -3223,17 +3409,15 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -3270,37 +3454,37 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -3311,10 +3495,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3322,7 +3506,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>80</v>
@@ -3334,23 +3518,19 @@
         <v>78</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>194</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3374,29 +3554,31 @@
         <v>78</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3408,35 +3590,37 @@
         <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>203</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>88</v>
@@ -3448,23 +3632,19 @@
         <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
@@ -3512,39 +3692,39 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>211</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3561,23 +3741,21 @@
         <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3602,13 +3780,13 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -3626,7 +3804,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3638,13 +3816,13 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -3655,10 +3833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3669,7 +3847,7 @@
         <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>78</v>
@@ -3678,16 +3856,16 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>220</v>
+        <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>134</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>135</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3726,51 +3904,51 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3778,7 +3956,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -3793,16 +3971,16 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3810,7 +3988,7 @@
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>78</v>
@@ -3828,11 +4006,13 @@
         <v>78</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>78</v>
@@ -3850,10 +4030,10 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>198</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>88</v>
@@ -3862,27 +4042,27 @@
         <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>233</v>
+        <v>131</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3902,16 +4082,16 @@
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3938,13 +4118,11 @@
         <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>78</v>
@@ -3962,7 +4140,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3980,7 +4158,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>131</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -3991,21 +4169,23 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
@@ -4017,17 +4197,15 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>241</v>
+        <v>133</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -4076,7 +4254,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>187</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4088,13 +4266,13 @@
         <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -4105,10 +4283,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4131,13 +4309,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4188,7 +4366,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4206,7 +4384,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4217,21 +4395,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4246,14 +4424,12 @@
         <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4290,19 +4466,19 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4320,7 +4496,7 @@
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4331,52 +4507,50 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>78</v>
@@ -4418,19 +4592,19 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>198</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4447,10 +4621,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4458,7 +4632,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>
@@ -4473,18 +4647,16 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>202</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
+        <v>203</v>
       </c>
       <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
-        <v>257</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -4520,20 +4692,22 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>88</v>
@@ -4545,34 +4719,32 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>260</v>
+        <v>131</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>215</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -4587,24 +4759,24 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>264</v>
+        <v>195</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>78</v>
@@ -4622,11 +4794,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>265</v>
+        <v>78</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -4644,7 +4818,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>198</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>88</v>
@@ -4656,27 +4830,27 @@
         <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>260</v>
+        <v>131</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4687,7 +4861,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -4699,13 +4873,13 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4756,7 +4930,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4768,13 +4942,13 @@
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>187</v>
+        <v>131</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -4785,14 +4959,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>221</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>157</v>
+        <v>222</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4805,7 +4979,7 @@
         <v>78</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>78</v>
@@ -4814,15 +4988,17 @@
         <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -4858,19 +5034,19 @@
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4888,7 +5064,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>187</v>
+        <v>131</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -4899,10 +5075,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4925,20 +5101,18 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
@@ -4986,7 +5160,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5004,21 +5178,21 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>203</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>235</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5026,7 +5200,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
@@ -5041,20 +5215,18 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
@@ -5078,13 +5250,13 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>78</v>
+        <v>240</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>78</v>
@@ -5102,7 +5274,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5117,28 +5289,26 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>211</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5159,18 +5329,16 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>277</v>
+        <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>255</v>
+        <v>179</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>257</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5218,10 +5386,10 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>253</v>
+        <v>181</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>88</v>
@@ -5230,38 +5398,38 @@
         <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>260</v>
+        <v>182</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
@@ -5273,18 +5441,18 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>279</v>
+        <v>133</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>280</v>
+        <v>247</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
@@ -5320,37 +5488,37 @@
         <v>78</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>187</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>283</v>
+        <v>182</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -5361,10 +5529,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>249</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>249</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5375,7 +5543,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5384,19 +5552,23 @@
         <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5420,13 +5592,11 @@
         <v>78</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -5444,13 +5614,13 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
@@ -5459,24 +5629,24 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>288</v>
+        <v>259</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5496,19 +5666,23 @@
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -5556,7 +5730,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>186</v>
+        <v>265</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5568,59 +5742,59 @@
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>187</v>
+        <v>266</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>189</v>
+        <v>269</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>160</v>
+        <v>271</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5646,49 +5820,49 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>78</v>
+        <v>255</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>78</v>
+        <v>272</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>192</v>
+        <v>268</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>187</v>
+        <v>274</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -5699,10 +5873,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5710,7 +5884,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
@@ -5725,13 +5899,13 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5782,7 +5956,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5797,24 +5971,24 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>78</v>
+        <v>279</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>78</v>
+        <v>281</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>78</v>
+        <v>282</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5822,7 +5996,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>88</v>
@@ -5834,18 +6008,20 @@
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>292</v>
+        <v>201</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -5870,13 +6046,11 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
@@ -5894,7 +6068,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -5909,24 +6083,24 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>78</v>
+        <v>290</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5946,16 +6120,16 @@
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6006,7 +6180,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6021,10 +6195,10 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6035,10 +6209,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6049,7 +6223,7 @@
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -6061,15 +6235,17 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>183</v>
+        <v>297</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>184</v>
+        <v>298</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -6118,25 +6294,25 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>186</v>
+        <v>296</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>187</v>
+        <v>301</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -6147,21 +6323,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -6173,17 +6349,15 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6232,25 +6406,25 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6261,14 +6435,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6281,26 +6455,24 @@
         <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6348,7 +6520,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>252</v>
+        <v>187</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6366,7 +6538,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -6377,42 +6549,46 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
@@ -6460,39 +6636,39 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>223</v>
+        <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>312</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6500,7 +6676,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>88</v>
@@ -6515,16 +6691,18 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -6560,22 +6738,20 @@
         <v>78</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>78</v>
+        <v>315</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>88</v>
@@ -6587,16 +6763,2172 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN46" t="s" s="2">
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
         <v>318</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Y48" s="2"/>
+      <c r="Z48" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="372">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:58:16+00:00</t>
+    <t>2026-08-13T09:15:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -767,10 +767,10 @@
     <t>Depending on the context of use, the code that was actually selected by the user (prescriber, dispenser, etc.) will have the coding.userSelected set to true.  As described in the coding datatype: "A coding may be marked as a "userSelected" if a user selected the particular coded value in a user interface (e.g. the user selects an item in a pick-list). If a user selected coding exists, it is the preferred choice for performing translations etc. Other codes can only be literal translations to alternative code systems, or codes at a lower level of granularity (e.g. a generic code for a vendor-specific primary one).</t>
   </si>
   <si>
-    <t>A coded concept that defines the type of a medication.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-medication-translation|2.2.0</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -789,76 +789,6 @@
     <t>RXO-1.1-Requested Give Code.code / RXE-2.1-Give Code.code / RXD-2.1-Dispense/Give Code.code / RXG-4.1-Give Code.code /RXA-5.1-Administered Code.code / RXC-2.1 Component Code</t>
   </si>
   <si>
-    <t>Medication.code.id</t>
-  </si>
-  <si>
-    <t>Medication.code.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Medication.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-medication-translation|2.2.0</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Medication.code.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
     <t>Medication.status</t>
   </si>
   <si>
@@ -972,6 +902,12 @@
     <t>Medication.ingredient.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t>Medication.ingredient.modifierExtension</t>
   </si>
   <si>
@@ -1058,6 +994,31 @@
     <t>Medication.ingredient.item[x].coding</t>
   </si>
   <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
     <t>Medication.ingredient.item[x]:itemCodeableConcept.text</t>
   </si>
   <si>
@@ -1065,6 +1026,24 @@
   </si>
   <si>
     <t>Nom de la substance</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
@@ -1513,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN65"/>
+  <dimension ref="A1:AN61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.796875" customWidth="true" bestFit="true"/>
@@ -5250,11 +5229,9 @@
         <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y33" t="s" s="2">
         <v>239</v>
       </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
         <v>240</v>
       </c>
@@ -5323,21 +5300,23 @@
         <v>78</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5362,13 +5341,13 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>78</v>
+        <v>239</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -5386,7 +5365,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>181</v>
+        <v>245</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5398,13 +5377,13 @@
         <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>182</v>
+        <v>251</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -5415,21 +5394,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
@@ -5438,20 +5417,18 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>133</v>
+        <v>253</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -5488,51 +5465,51 @@
         <v>78</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>182</v>
+        <v>257</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5543,7 +5520,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -5552,23 +5529,21 @@
         <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5592,11 +5567,11 @@
         <v>78</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -5614,13 +5589,13 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>78</v>
@@ -5629,24 +5604,24 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5669,20 +5644,16 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>178</v>
+        <v>269</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -5730,7 +5701,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5748,21 +5719,21 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5773,28 +5744,28 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5820,37 +5791,37 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="Z38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AA38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>78</v>
@@ -5862,7 +5833,7 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -5873,10 +5844,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5896,16 +5867,16 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>276</v>
+        <v>178</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>277</v>
+        <v>179</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>278</v>
+        <v>180</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5956,7 +5927,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5968,38 +5939,38 @@
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>280</v>
+        <v>182</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>281</v>
+        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>282</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -6011,16 +5982,16 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>201</v>
+        <v>133</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>286</v>
+        <v>225</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6046,11 +6017,13 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="Y40" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
@@ -6068,71 +6041,75 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>283</v>
+        <v>187</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>289</v>
+        <v>182</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>290</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>292</v>
+        <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6180,25 +6157,25 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>295</v>
+        <v>131</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -6209,10 +6186,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6220,10 +6197,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -6235,18 +6212,18 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
       </c>
@@ -6282,25 +6259,23 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
@@ -6309,26 +6284,28 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6349,16 +6326,18 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>178</v>
+        <v>299</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>179</v>
+        <v>290</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>180</v>
+        <v>291</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6406,10 +6385,10 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>181</v>
+        <v>288</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>88</v>
@@ -6418,38 +6397,40 @@
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="D44" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -6461,18 +6442,18 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>247</v>
+        <v>302</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6496,13 +6477,11 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -6520,31 +6499,31 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>187</v>
+        <v>288</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45">
@@ -6552,43 +6531,39 @@
         <v>304</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>305</v>
+        <v>78</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>306</v>
+        <v>179</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
@@ -6636,25 +6611,25 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>308</v>
+        <v>181</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -6665,21 +6640,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>78</v>
@@ -6691,18 +6666,18 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -6738,53 +6713,53 @@
         <v>78</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>315</v>
+        <v>137</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>309</v>
+        <v>187</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>241</v>
+        <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>316</v>
+        <v>182</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>317</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="C47" t="s" s="2">
-        <v>319</v>
-      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>78</v>
       </c>
@@ -6793,7 +6768,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -6802,10 +6777,10 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>311</v>
@@ -6813,9 +6788,11 @@
       <c r="M47" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N47" s="2"/>
+      <c r="N47" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -6864,13 +6841,13 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
@@ -6879,7 +6856,7 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>241</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>316</v>
@@ -6893,14 +6870,12 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>78</v>
       </c>
@@ -6918,20 +6893,22 @@
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -6956,32 +6933,34 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AA48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>309</v>
-      </c>
       <c r="AG48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>88</v>
@@ -6993,24 +6972,24 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>241</v>
+        <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7033,16 +7012,18 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>178</v>
+        <v>328</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>179</v>
+        <v>329</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>180</v>
+        <v>330</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7090,7 +7071,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>181</v>
+        <v>327</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7102,13 +7083,13 @@
         <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7119,21 +7100,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>78</v>
@@ -7145,17 +7126,15 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>133</v>
+        <v>269</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>247</v>
+        <v>334</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7192,51 +7171,51 @@
         <v>78</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>187</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>78</v>
+        <v>336</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7247,7 +7226,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>78</v>
@@ -7256,23 +7235,19 @@
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>250</v>
+        <v>178</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>251</v>
+        <v>179</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7320,50 +7295,50 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>257</v>
+        <v>181</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -7372,23 +7347,21 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>333</v>
+        <v>281</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7424,53 +7397,55 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>265</v>
+        <v>187</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>266</v>
+        <v>182</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>78</v>
       </c>
@@ -7491,18 +7466,16 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -7550,25 +7523,25 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>334</v>
+        <v>187</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -7579,10 +7552,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7602,16 +7575,16 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>292</v>
+        <v>214</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7662,7 +7635,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7677,24 +7650,24 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>343</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>295</v>
+        <v>349</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7714,16 +7687,16 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>179</v>
+        <v>351</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>180</v>
+        <v>352</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7774,7 +7747,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>181</v>
+        <v>353</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7786,13 +7759,13 @@
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>182</v>
+        <v>354</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -7803,21 +7776,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -7829,17 +7802,15 @@
         <v>78</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>133</v>
+        <v>274</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>247</v>
+        <v>356</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -7876,37 +7847,37 @@
         <v>78</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>186</v>
+        <v>78</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>187</v>
+        <v>355</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>182</v>
+        <v>358</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -7917,14 +7888,12 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>78</v>
       </c>
@@ -7945,13 +7914,13 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>349</v>
+        <v>178</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>350</v>
+        <v>179</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>351</v>
+        <v>180</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8002,25 +7971,25 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8031,21 +8000,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
@@ -8054,18 +8023,20 @@
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>214</v>
+        <v>133</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>353</v>
+        <v>281</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8114,25 +8085,25 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>355</v>
+        <v>187</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>356</v>
+        <v>182</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8143,42 +8114,46 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>214</v>
+        <v>133</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>358</v>
+        <v>285</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -8226,25 +8201,25 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>360</v>
+        <v>287</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>361</v>
+        <v>131</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -8281,7 +8256,7 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>297</v>
+        <v>178</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>363</v>
@@ -8353,16 +8328,16 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="61">
@@ -8393,13 +8368,13 @@
         <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>179</v>
+        <v>368</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>180</v>
+        <v>369</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8450,7 +8425,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>181</v>
+        <v>366</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8462,473 +8437,19 @@
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>182</v>
+        <v>370</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M64" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:15:12+00:00</t>
+    <t>2026-08-13T09:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:41:50+00:00</t>
+    <t>2026-08-13T12:00:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T12:00:16+00:00</t>
+    <t>2026-08-13T12:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -770,7 +770,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-medication-translation|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-medication|2.2.0</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -1520,7 +1520,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="47.4921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.2421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.7421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
